--- a/backend/app/templates/material_inspection_form.xlsx
+++ b/backend/app/templates/material_inspection_form.xlsx
@@ -3410,7 +3410,7 @@
       <c r="I80" s="127" t="n"/>
       <c r="J80" s="127" t="n"/>
     </row>
-    <row r="81" ht="283.35" customHeight="1" s="118">
+    <row r="81" ht="269.29" customHeight="1" s="118">
       <c r="A81" s="112" t="n"/>
       <c r="B81" s="160" t="n"/>
       <c r="C81" s="160" t="n"/>
@@ -3474,7 +3474,7 @@
       <c r="I83" s="166" t="n"/>
       <c r="J83" s="165" t="n"/>
     </row>
-    <row r="84" ht="283.35" customHeight="1" s="118">
+    <row r="84" ht="269.29" customHeight="1" s="118">
       <c r="A84" s="112" t="n"/>
       <c r="B84" s="160" t="n"/>
       <c r="C84" s="160" t="n"/>
